--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260827.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260827.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>314,672</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,343,000</t>
+          <t>314,672</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>1,343,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,005,822</t>
+          <t>811,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>811,897</t>
+          <t>1,005,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,194,249</t>
+          <t>4,469,578</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,469,578</t>
+          <t>7,194,249</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,383,384</t>
+          <t>2,606,703</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,606,703</t>
+          <t>1,383,384</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>4,977,956</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>4,977,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,006,121</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>1,006,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>1,764,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
